--- a/RTM_ ECommerce_Testing_Project.xlsx
+++ b/RTM_ ECommerce_Testing_Project.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="52">
   <si>
     <t>Req ID</t>
   </si>
@@ -25,7 +25,10 @@
     <t>Test Case ID</t>
   </si>
   <si>
-    <t>Status</t>
+    <t>Execution Result</t>
+  </si>
+  <si>
+    <t>BUG ID</t>
   </si>
   <si>
     <t>REQ_001</t>
@@ -40,7 +43,10 @@
     <t>TC_001</t>
   </si>
   <si>
-    <t>Pending</t>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>_</t>
   </si>
   <si>
     <t>REQ_002</t>
@@ -134,6 +140,12 @@
   </si>
   <si>
     <t>TC_010</t>
+  </si>
+  <si>
+    <t>Fail — Bug KAN-5, KAN-6</t>
+  </si>
+  <si>
+    <t>KAN-5, KAN-6, KAN-7, KAN-8</t>
   </si>
   <si>
     <t>REQ_011</t>
@@ -161,7 +173,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -181,6 +193,12 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="13.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -190,7 +208,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border/>
     <border>
       <left style="thick">
@@ -199,6 +217,28 @@
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
@@ -210,15 +250,26 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -442,7 +493,8 @@
     <col customWidth="1" min="3" max="3" width="44.5"/>
     <col customWidth="1" min="4" max="4" width="14.5"/>
     <col customWidth="1" min="5" max="5" width="13.13"/>
-    <col customWidth="1" min="6" max="6" width="8.63"/>
+    <col customWidth="1" min="6" max="6" width="24.38"/>
+    <col customWidth="1" min="7" max="7" width="30.13"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -461,223 +513,249 @@
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
